--- a/vse-loti/340755569/spec-340755569.xlsx
+++ b/vse-loti/340755569/spec-340755569.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,6 +95,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -463,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -592,18 +595,25 @@
         <v>10928919.82</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>НДС 22 %, ставка из документа: "имость ответственного хранения составляет 7,47 рублей/м2, в том числе НДС 22 %, в размере 1,35 рублей/м2 , за каждые сутки хранения." — Проект договора.txt; суммы источника указаны без НДС: "Цена за единицу (предложение участника) без НДС" — 226064_720.26.00773_КОММ.txt. «без НДС» — сумма из документа, «с НДС» = сумма × 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Источник: 226064_720.26.00773_КОММ.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:B9"/>
+    <mergeCell ref="A8:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/340755569/spec-340755569.xlsx
+++ b/vse-loti/340755569/spec-340755569.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -513,17 +514,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -553,13 +559,16 @@
         <v>4.9</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>1828190</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>8958131</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>1828190</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>2230391.8</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>10928919.82</v>
       </c>
     </row>
     <row r="3">
@@ -572,7 +581,16 @@
         <v>4.9</v>
       </c>
       <c r="G3" s="8" t="n">
+        <v>1828190</v>
+      </c>
+      <c r="H3" s="8" t="n">
         <v>8958131</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>2230391.8</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>10928919.82</v>
       </c>
     </row>
     <row r="4">
@@ -581,7 +599,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="H4" s="8" t="n">
         <v>8958131</v>
       </c>
     </row>
@@ -591,7 +609,7 @@
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="J5" s="8" t="n">
         <v>10928919.82</v>
       </c>
     </row>
